--- a/test_output_report.xlsx
+++ b/test_output_report.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-04-27 12:15</t>
+          <t>2026-04-27 12:19</t>
         </is>
       </c>
     </row>
